--- a/data/kz/niches/niche_formats_PHARMACY.xlsx
+++ b/data/kz/niches/niche_formats_PHARMACY.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -590,12 +591,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -641,12 +642,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -717,6 +718,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -772,12 +774,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -814,12 +816,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -852,12 +854,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -922,6 +924,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -972,12 +975,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1005,12 +1008,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1073,6 +1076,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1172,6 +1176,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1486,6 +1491,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1611,6 +1617,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1691,12 +1698,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1750,12 +1757,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1855,6 +1862,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1975,12 +1983,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2050,12 +2058,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2161,6 +2169,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2231,12 +2240,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2278,12 +2287,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2357,6 +2366,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2427,12 +2437,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2472,12 +2482,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2550,6 +2560,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2605,12 +2616,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2647,12 +2658,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2725,6 +2736,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2795,12 +2807,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2856,12 +2868,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2948,6 +2960,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2993,12 +3006,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3027,12 +3040,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3061,12 +3074,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3095,12 +3108,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_MINI</t>
+          <t>PHARMACY_SOLO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3156,6 +3169,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3181,12 +3195,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3203,12 +3217,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PHARMA_STD</t>
+          <t>PHARMACY_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
